--- a/docs/YOTA_Backend_Development_Plan.xlsx
+++ b/docs/YOTA_Backend_Development_Plan.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="📋 工作項主表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="🗓 里程碑總覽" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="🔌 API 清單" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="📊 統計儀表板" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="📅 甘特圖" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="🗓 里程碑總覽" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="🔌 API 清單" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="📊 統計儀表板" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,8 +93,97 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF333333"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFE74C3C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF375623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFE67E22"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF843C00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF2980B9"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF27AE60"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF8E44AD"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF333333"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="27">
     <fill>
       <patternFill/>
     </fill>
@@ -165,8 +255,68 @@
         <fgColor rgb="FFFFD7D7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7D31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF843C00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE74C3C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE67E22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2980B9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27AE60"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8E44AD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -188,11 +338,25 @@
         <color rgb="FFD0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF666666"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,6 +455,169 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4412,6 +4739,2588 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00833C00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="4.2" customWidth="1" min="7" max="7"/>
+    <col width="4.2" customWidth="1" min="8" max="8"/>
+    <col width="4.2" customWidth="1" min="9" max="9"/>
+    <col width="4.2" customWidth="1" min="10" max="10"/>
+    <col width="4.2" customWidth="1" min="11" max="11"/>
+    <col width="4.2" customWidth="1" min="12" max="12"/>
+    <col width="4.2" customWidth="1" min="13" max="13"/>
+    <col width="4.2" customWidth="1" min="14" max="14"/>
+    <col width="4.2" customWidth="1" min="15" max="15"/>
+    <col width="4.2" customWidth="1" min="16" max="16"/>
+    <col width="4.2" customWidth="1" min="17" max="17"/>
+    <col width="4.2" customWidth="1" min="18" max="18"/>
+    <col width="4.2" customWidth="1" min="19" max="19"/>
+    <col width="4.2" customWidth="1" min="20" max="20"/>
+    <col width="4.2" customWidth="1" min="21" max="21"/>
+    <col width="4.2" customWidth="1" min="22" max="22"/>
+    <col width="4.2" customWidth="1" min="23" max="23"/>
+    <col width="4.2" customWidth="1" min="24" max="24"/>
+    <col width="4.2" customWidth="1" min="25" max="25"/>
+    <col width="4.2" customWidth="1" min="26" max="26"/>
+    <col width="4.2" customWidth="1" min="27" max="27"/>
+    <col width="4.2" customWidth="1" min="28" max="28"/>
+    <col width="4.2" customWidth="1" min="29" max="29"/>
+    <col width="4.2" customWidth="1" min="30" max="30"/>
+    <col width="4.2" customWidth="1" min="31" max="31"/>
+    <col width="4.2" customWidth="1" min="32" max="32"/>
+    <col width="4.2" customWidth="1" min="33" max="33"/>
+    <col width="4.2" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>YOTA 後台後端開發甘特圖　開始 2026/04/11（週一）· 28 週 · 預計完成 2026/10/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="B2" s="35" t="inlineStr">
+        <is>
+          <t>工作群組</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>優先序</t>
+        </is>
+      </c>
+      <c r="D2" s="35" t="inlineStr">
+        <is>
+          <t>負責人</t>
+        </is>
+      </c>
+      <c r="E2" s="35" t="inlineStr">
+        <is>
+          <t>開始</t>
+        </is>
+      </c>
+      <c r="F2" s="35" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="G2" s="36" t="inlineStr">
+        <is>
+          <t>4月 April</t>
+        </is>
+      </c>
+      <c r="H2" s="37" t="n"/>
+      <c r="I2" s="37" t="n"/>
+      <c r="J2" s="38" t="inlineStr">
+        <is>
+          <t>5月 May</t>
+        </is>
+      </c>
+      <c r="K2" s="39" t="n"/>
+      <c r="L2" s="39" t="n"/>
+      <c r="M2" s="39" t="n"/>
+      <c r="N2" s="39" t="n"/>
+      <c r="O2" s="40" t="inlineStr">
+        <is>
+          <t>6月 June</t>
+        </is>
+      </c>
+      <c r="P2" s="41" t="n"/>
+      <c r="Q2" s="41" t="n"/>
+      <c r="R2" s="41" t="n"/>
+      <c r="S2" s="42" t="inlineStr">
+        <is>
+          <t>7月 July</t>
+        </is>
+      </c>
+      <c r="T2" s="43" t="n"/>
+      <c r="U2" s="43" t="n"/>
+      <c r="V2" s="43" t="n"/>
+      <c r="W2" s="36" t="inlineStr">
+        <is>
+          <t>8月 Aug</t>
+        </is>
+      </c>
+      <c r="X2" s="37" t="n"/>
+      <c r="Y2" s="37" t="n"/>
+      <c r="Z2" s="37" t="n"/>
+      <c r="AA2" s="37" t="n"/>
+      <c r="AB2" s="38" t="inlineStr">
+        <is>
+          <t>9月 Sep</t>
+        </is>
+      </c>
+      <c r="AC2" s="39" t="n"/>
+      <c r="AD2" s="39" t="n"/>
+      <c r="AE2" s="39" t="n"/>
+      <c r="AF2" s="40" t="inlineStr">
+        <is>
+          <t>10月 Oct</t>
+        </is>
+      </c>
+      <c r="AG2" s="41" t="n"/>
+      <c r="AH2" s="41" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="44" t="n"/>
+      <c r="B3" s="44" t="n"/>
+      <c r="C3" s="44" t="n"/>
+      <c r="D3" s="44" t="n"/>
+      <c r="E3" s="44" t="n"/>
+      <c r="F3" s="44" t="n"/>
+      <c r="G3" s="45" t="inlineStr">
+        <is>
+          <t>W1
+4/11</t>
+        </is>
+      </c>
+      <c r="H3" s="45" t="inlineStr">
+        <is>
+          <t>W2
+4/18</t>
+        </is>
+      </c>
+      <c r="I3" s="46" t="inlineStr">
+        <is>
+          <t>W3
+4/25</t>
+        </is>
+      </c>
+      <c r="J3" s="47" t="inlineStr">
+        <is>
+          <t>W4
+5/2</t>
+        </is>
+      </c>
+      <c r="K3" s="47" t="inlineStr">
+        <is>
+          <t>W5
+5/9</t>
+        </is>
+      </c>
+      <c r="L3" s="48" t="inlineStr">
+        <is>
+          <t>W6
+5/16</t>
+        </is>
+      </c>
+      <c r="M3" s="47" t="inlineStr">
+        <is>
+          <t>W7
+5/23</t>
+        </is>
+      </c>
+      <c r="N3" s="47" t="inlineStr">
+        <is>
+          <t>W8
+5/30</t>
+        </is>
+      </c>
+      <c r="O3" s="49" t="inlineStr">
+        <is>
+          <t>W9
+6/6</t>
+        </is>
+      </c>
+      <c r="P3" s="50" t="inlineStr">
+        <is>
+          <t>W10
+6/13</t>
+        </is>
+      </c>
+      <c r="Q3" s="49" t="inlineStr">
+        <is>
+          <t>W11
+6/20</t>
+        </is>
+      </c>
+      <c r="R3" s="49" t="inlineStr">
+        <is>
+          <t>W12
+6/27</t>
+        </is>
+      </c>
+      <c r="S3" s="51" t="inlineStr">
+        <is>
+          <t>W13
+7/4</t>
+        </is>
+      </c>
+      <c r="T3" s="52" t="inlineStr">
+        <is>
+          <t>W14
+7/11</t>
+        </is>
+      </c>
+      <c r="U3" s="52" t="inlineStr">
+        <is>
+          <t>W15
+7/18</t>
+        </is>
+      </c>
+      <c r="V3" s="52" t="inlineStr">
+        <is>
+          <t>W16
+7/25</t>
+        </is>
+      </c>
+      <c r="W3" s="46" t="inlineStr">
+        <is>
+          <t>W17
+8/1</t>
+        </is>
+      </c>
+      <c r="X3" s="45" t="inlineStr">
+        <is>
+          <t>W18
+8/8</t>
+        </is>
+      </c>
+      <c r="Y3" s="45" t="inlineStr">
+        <is>
+          <t>W19
+8/15</t>
+        </is>
+      </c>
+      <c r="Z3" s="45" t="inlineStr">
+        <is>
+          <t>W20
+8/22</t>
+        </is>
+      </c>
+      <c r="AA3" s="46" t="inlineStr">
+        <is>
+          <t>W21
+8/29</t>
+        </is>
+      </c>
+      <c r="AB3" s="47" t="inlineStr">
+        <is>
+          <t>W22
+9/5</t>
+        </is>
+      </c>
+      <c r="AC3" s="47" t="inlineStr">
+        <is>
+          <t>W23
+9/12</t>
+        </is>
+      </c>
+      <c r="AD3" s="48" t="inlineStr">
+        <is>
+          <t>W24
+9/19</t>
+        </is>
+      </c>
+      <c r="AE3" s="47" t="inlineStr">
+        <is>
+          <t>W25
+9/26</t>
+        </is>
+      </c>
+      <c r="AF3" s="49" t="inlineStr">
+        <is>
+          <t>W26
+10/3</t>
+        </is>
+      </c>
+      <c r="AG3" s="49" t="inlineStr">
+        <is>
+          <t>W27
+10/10</t>
+        </is>
+      </c>
+      <c r="AH3" s="50" t="inlineStr">
+        <is>
+          <t>W28
+10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="53" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>基礎平台 #1-5</t>
+        </is>
+      </c>
+      <c r="C4" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E4" s="56" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+      <c r="F4" s="56" t="inlineStr">
+        <is>
+          <t>4/22</t>
+        </is>
+      </c>
+      <c r="G4" s="57" t="n"/>
+      <c r="H4" s="57" t="n"/>
+      <c r="I4" s="58" t="n"/>
+      <c r="J4" s="59" t="n"/>
+      <c r="K4" s="59" t="n"/>
+      <c r="L4" s="59" t="n"/>
+      <c r="M4" s="59" t="n"/>
+      <c r="N4" s="59" t="n"/>
+      <c r="O4" s="60" t="n"/>
+      <c r="P4" s="60" t="n"/>
+      <c r="Q4" s="60" t="n"/>
+      <c r="R4" s="60" t="n"/>
+      <c r="S4" s="61" t="n"/>
+      <c r="T4" s="61" t="n"/>
+      <c r="U4" s="61" t="n"/>
+      <c r="V4" s="61" t="n"/>
+      <c r="W4" s="62" t="n"/>
+      <c r="X4" s="62" t="n"/>
+      <c r="Y4" s="62" t="n"/>
+      <c r="Z4" s="62" t="n"/>
+      <c r="AA4" s="62" t="n"/>
+      <c r="AB4" s="59" t="n"/>
+      <c r="AC4" s="59" t="n"/>
+      <c r="AD4" s="59" t="n"/>
+      <c r="AE4" s="59" t="n"/>
+      <c r="AF4" s="60" t="n"/>
+      <c r="AG4" s="60" t="n"/>
+      <c r="AH4" s="60" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="53" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B5" s="54" t="inlineStr">
+        <is>
+          <t>Auth + Token #6-8</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E5" s="56" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+      <c r="F5" s="56" t="inlineStr">
+        <is>
+          <t>4/22</t>
+        </is>
+      </c>
+      <c r="G5" s="57" t="n"/>
+      <c r="H5" s="57" t="n"/>
+      <c r="I5" s="58" t="n"/>
+      <c r="J5" s="59" t="n"/>
+      <c r="K5" s="59" t="n"/>
+      <c r="L5" s="59" t="n"/>
+      <c r="M5" s="59" t="n"/>
+      <c r="N5" s="59" t="n"/>
+      <c r="O5" s="60" t="n"/>
+      <c r="P5" s="60" t="n"/>
+      <c r="Q5" s="60" t="n"/>
+      <c r="R5" s="60" t="n"/>
+      <c r="S5" s="61" t="n"/>
+      <c r="T5" s="61" t="n"/>
+      <c r="U5" s="61" t="n"/>
+      <c r="V5" s="61" t="n"/>
+      <c r="W5" s="62" t="n"/>
+      <c r="X5" s="62" t="n"/>
+      <c r="Y5" s="62" t="n"/>
+      <c r="Z5" s="62" t="n"/>
+      <c r="AA5" s="62" t="n"/>
+      <c r="AB5" s="59" t="n"/>
+      <c r="AC5" s="59" t="n"/>
+      <c r="AD5" s="59" t="n"/>
+      <c r="AE5" s="59" t="n"/>
+      <c r="AF5" s="60" t="n"/>
+      <c r="AG5" s="60" t="n"/>
+      <c r="AH5" s="60" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>RBAC + 權限機制 #9-10</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D6" s="56" t="inlineStr">
+        <is>
+          <t>Lead/後端C</t>
+        </is>
+      </c>
+      <c r="E6" s="56" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+      <c r="F6" s="56" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+      <c r="G6" s="62" t="n"/>
+      <c r="H6" s="57" t="n"/>
+      <c r="I6" s="63" t="n"/>
+      <c r="J6" s="59" t="n"/>
+      <c r="K6" s="59" t="n"/>
+      <c r="L6" s="59" t="n"/>
+      <c r="M6" s="59" t="n"/>
+      <c r="N6" s="59" t="n"/>
+      <c r="O6" s="60" t="n"/>
+      <c r="P6" s="60" t="n"/>
+      <c r="Q6" s="60" t="n"/>
+      <c r="R6" s="60" t="n"/>
+      <c r="S6" s="61" t="n"/>
+      <c r="T6" s="61" t="n"/>
+      <c r="U6" s="61" t="n"/>
+      <c r="V6" s="61" t="n"/>
+      <c r="W6" s="62" t="n"/>
+      <c r="X6" s="62" t="n"/>
+      <c r="Y6" s="62" t="n"/>
+      <c r="Z6" s="62" t="n"/>
+      <c r="AA6" s="62" t="n"/>
+      <c r="AB6" s="59" t="n"/>
+      <c r="AC6" s="59" t="n"/>
+      <c r="AD6" s="59" t="n"/>
+      <c r="AE6" s="59" t="n"/>
+      <c r="AF6" s="60" t="n"/>
+      <c r="AG6" s="60" t="n"/>
+      <c r="AH6" s="60" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B7" s="54" t="inlineStr">
+        <is>
+          <t>Operators 帳號管理 #16-17</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D7" s="56" t="inlineStr">
+        <is>
+          <t>後端A</t>
+        </is>
+      </c>
+      <c r="E7" s="56" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+      <c r="F7" s="56" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+      <c r="G7" s="62" t="n"/>
+      <c r="H7" s="57" t="n"/>
+      <c r="I7" s="63" t="n"/>
+      <c r="J7" s="59" t="n"/>
+      <c r="K7" s="59" t="n"/>
+      <c r="L7" s="59" t="n"/>
+      <c r="M7" s="59" t="n"/>
+      <c r="N7" s="59" t="n"/>
+      <c r="O7" s="60" t="n"/>
+      <c r="P7" s="60" t="n"/>
+      <c r="Q7" s="60" t="n"/>
+      <c r="R7" s="60" t="n"/>
+      <c r="S7" s="61" t="n"/>
+      <c r="T7" s="61" t="n"/>
+      <c r="U7" s="61" t="n"/>
+      <c r="V7" s="61" t="n"/>
+      <c r="W7" s="62" t="n"/>
+      <c r="X7" s="62" t="n"/>
+      <c r="Y7" s="62" t="n"/>
+      <c r="Z7" s="62" t="n"/>
+      <c r="AA7" s="62" t="n"/>
+      <c r="AB7" s="59" t="n"/>
+      <c r="AC7" s="59" t="n"/>
+      <c r="AD7" s="59" t="n"/>
+      <c r="AE7" s="59" t="n"/>
+      <c r="AF7" s="60" t="n"/>
+      <c r="AG7" s="60" t="n"/>
+      <c r="AH7" s="60" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>Security IP白名單 建表 #11(P0)</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D8" s="56" t="inlineStr">
+        <is>
+          <t>後端C</t>
+        </is>
+      </c>
+      <c r="E8" s="56" t="inlineStr">
+        <is>
+          <t>4/25</t>
+        </is>
+      </c>
+      <c r="F8" s="56" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+      <c r="G8" s="62" t="n"/>
+      <c r="H8" s="62" t="n"/>
+      <c r="I8" s="64" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="J8" s="59" t="n"/>
+      <c r="K8" s="59" t="n"/>
+      <c r="L8" s="59" t="n"/>
+      <c r="M8" s="59" t="n"/>
+      <c r="N8" s="59" t="n"/>
+      <c r="O8" s="60" t="n"/>
+      <c r="P8" s="60" t="n"/>
+      <c r="Q8" s="60" t="n"/>
+      <c r="R8" s="60" t="n"/>
+      <c r="S8" s="61" t="n"/>
+      <c r="T8" s="61" t="n"/>
+      <c r="U8" s="61" t="n"/>
+      <c r="V8" s="61" t="n"/>
+      <c r="W8" s="62" t="n"/>
+      <c r="X8" s="62" t="n"/>
+      <c r="Y8" s="62" t="n"/>
+      <c r="Z8" s="62" t="n"/>
+      <c r="AA8" s="62" t="n"/>
+      <c r="AB8" s="59" t="n"/>
+      <c r="AC8" s="59" t="n"/>
+      <c r="AD8" s="59" t="n"/>
+      <c r="AE8" s="59" t="n"/>
+      <c r="AF8" s="60" t="n"/>
+      <c r="AG8" s="60" t="n"/>
+      <c r="AH8" s="60" t="n"/>
+    </row>
+    <row r="9" ht="4" customHeight="1">
+      <c r="A9" s="65" t="n"/>
+      <c r="B9" s="65" t="n"/>
+      <c r="C9" s="65" t="n"/>
+      <c r="D9" s="65" t="n"/>
+      <c r="E9" s="65" t="n"/>
+      <c r="F9" s="65" t="n"/>
+      <c r="G9" s="65" t="n"/>
+      <c r="H9" s="65" t="n"/>
+      <c r="I9" s="65" t="n"/>
+      <c r="J9" s="65" t="n"/>
+      <c r="K9" s="65" t="n"/>
+      <c r="L9" s="65" t="n"/>
+      <c r="M9" s="65" t="n"/>
+      <c r="N9" s="65" t="n"/>
+      <c r="O9" s="65" t="n"/>
+      <c r="P9" s="65" t="n"/>
+      <c r="Q9" s="65" t="n"/>
+      <c r="R9" s="65" t="n"/>
+      <c r="S9" s="65" t="n"/>
+      <c r="T9" s="65" t="n"/>
+      <c r="U9" s="65" t="n"/>
+      <c r="V9" s="65" t="n"/>
+      <c r="W9" s="65" t="n"/>
+      <c r="X9" s="65" t="n"/>
+      <c r="Y9" s="65" t="n"/>
+      <c r="Z9" s="65" t="n"/>
+      <c r="AA9" s="65" t="n"/>
+      <c r="AB9" s="65" t="n"/>
+      <c r="AC9" s="65" t="n"/>
+      <c r="AD9" s="65" t="n"/>
+      <c r="AE9" s="65" t="n"/>
+      <c r="AF9" s="65" t="n"/>
+      <c r="AG9" s="65" t="n"/>
+      <c r="AH9" s="65" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="53" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>Members P0 #20-22</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t>後端A</t>
+        </is>
+      </c>
+      <c r="E10" s="56" t="inlineStr">
+        <is>
+          <t>5/2</t>
+        </is>
+      </c>
+      <c r="F10" s="56" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+      <c r="G10" s="62" t="n"/>
+      <c r="H10" s="62" t="n"/>
+      <c r="I10" s="62" t="n"/>
+      <c r="J10" s="57" t="n"/>
+      <c r="K10" s="57" t="n"/>
+      <c r="L10" s="66" t="n"/>
+      <c r="M10" s="59" t="n"/>
+      <c r="N10" s="59" t="n"/>
+      <c r="O10" s="60" t="n"/>
+      <c r="P10" s="60" t="n"/>
+      <c r="Q10" s="60" t="n"/>
+      <c r="R10" s="60" t="n"/>
+      <c r="S10" s="61" t="n"/>
+      <c r="T10" s="61" t="n"/>
+      <c r="U10" s="61" t="n"/>
+      <c r="V10" s="61" t="n"/>
+      <c r="W10" s="62" t="n"/>
+      <c r="X10" s="62" t="n"/>
+      <c r="Y10" s="62" t="n"/>
+      <c r="Z10" s="62" t="n"/>
+      <c r="AA10" s="62" t="n"/>
+      <c r="AB10" s="59" t="n"/>
+      <c r="AC10" s="59" t="n"/>
+      <c r="AD10" s="59" t="n"/>
+      <c r="AE10" s="59" t="n"/>
+      <c r="AF10" s="60" t="n"/>
+      <c r="AG10" s="60" t="n"/>
+      <c r="AH10" s="60" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>Finance 總覽 + 提款帳戶 #27,27-1</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D11" s="56" t="inlineStr">
+        <is>
+          <t>後端B</t>
+        </is>
+      </c>
+      <c r="E11" s="56" t="inlineStr">
+        <is>
+          <t>5/2</t>
+        </is>
+      </c>
+      <c r="F11" s="56" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="G11" s="62" t="n"/>
+      <c r="H11" s="62" t="n"/>
+      <c r="I11" s="62" t="n"/>
+      <c r="J11" s="57" t="n"/>
+      <c r="K11" s="59" t="n"/>
+      <c r="L11" s="66" t="n"/>
+      <c r="M11" s="59" t="n"/>
+      <c r="N11" s="59" t="n"/>
+      <c r="O11" s="60" t="n"/>
+      <c r="P11" s="60" t="n"/>
+      <c r="Q11" s="60" t="n"/>
+      <c r="R11" s="60" t="n"/>
+      <c r="S11" s="61" t="n"/>
+      <c r="T11" s="61" t="n"/>
+      <c r="U11" s="61" t="n"/>
+      <c r="V11" s="61" t="n"/>
+      <c r="W11" s="62" t="n"/>
+      <c r="X11" s="62" t="n"/>
+      <c r="Y11" s="62" t="n"/>
+      <c r="Z11" s="62" t="n"/>
+      <c r="AA11" s="62" t="n"/>
+      <c r="AB11" s="59" t="n"/>
+      <c r="AC11" s="59" t="n"/>
+      <c r="AD11" s="59" t="n"/>
+      <c r="AE11" s="59" t="n"/>
+      <c r="AF11" s="60" t="n"/>
+      <c r="AG11" s="60" t="n"/>
+      <c r="AH11" s="60" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="53" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>Finance 存提款 + 鎖單 #28-32</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="inlineStr">
+        <is>
+          <t>後端B</t>
+        </is>
+      </c>
+      <c r="E12" s="56" t="inlineStr">
+        <is>
+          <t>5/2</t>
+        </is>
+      </c>
+      <c r="F12" s="56" t="inlineStr">
+        <is>
+          <t>5/20</t>
+        </is>
+      </c>
+      <c r="G12" s="62" t="n"/>
+      <c r="H12" s="62" t="n"/>
+      <c r="I12" s="62" t="n"/>
+      <c r="J12" s="57" t="n"/>
+      <c r="K12" s="57" t="n"/>
+      <c r="L12" s="63" t="n"/>
+      <c r="M12" s="59" t="n"/>
+      <c r="N12" s="59" t="n"/>
+      <c r="O12" s="60" t="n"/>
+      <c r="P12" s="60" t="n"/>
+      <c r="Q12" s="60" t="n"/>
+      <c r="R12" s="60" t="n"/>
+      <c r="S12" s="61" t="n"/>
+      <c r="T12" s="61" t="n"/>
+      <c r="U12" s="61" t="n"/>
+      <c r="V12" s="61" t="n"/>
+      <c r="W12" s="62" t="n"/>
+      <c r="X12" s="62" t="n"/>
+      <c r="Y12" s="62" t="n"/>
+      <c r="Z12" s="62" t="n"/>
+      <c r="AA12" s="62" t="n"/>
+      <c r="AB12" s="59" t="n"/>
+      <c r="AC12" s="59" t="n"/>
+      <c r="AD12" s="59" t="n"/>
+      <c r="AE12" s="59" t="n"/>
+      <c r="AF12" s="60" t="n"/>
+      <c r="AG12" s="60" t="n"/>
+      <c r="AH12" s="60" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="53" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>Finance 資金流水 #32</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t>後端B</t>
+        </is>
+      </c>
+      <c r="E13" s="56" t="inlineStr">
+        <is>
+          <t>5/9</t>
+        </is>
+      </c>
+      <c r="F13" s="56" t="inlineStr">
+        <is>
+          <t>5/20</t>
+        </is>
+      </c>
+      <c r="G13" s="62" t="n"/>
+      <c r="H13" s="62" t="n"/>
+      <c r="I13" s="62" t="n"/>
+      <c r="J13" s="59" t="n"/>
+      <c r="K13" s="57" t="n"/>
+      <c r="L13" s="64" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="M13" s="59" t="n"/>
+      <c r="N13" s="59" t="n"/>
+      <c r="O13" s="60" t="n"/>
+      <c r="P13" s="60" t="n"/>
+      <c r="Q13" s="60" t="n"/>
+      <c r="R13" s="60" t="n"/>
+      <c r="S13" s="61" t="n"/>
+      <c r="T13" s="61" t="n"/>
+      <c r="U13" s="61" t="n"/>
+      <c r="V13" s="61" t="n"/>
+      <c r="W13" s="62" t="n"/>
+      <c r="X13" s="62" t="n"/>
+      <c r="Y13" s="62" t="n"/>
+      <c r="Z13" s="62" t="n"/>
+      <c r="AA13" s="62" t="n"/>
+      <c r="AB13" s="59" t="n"/>
+      <c r="AC13" s="59" t="n"/>
+      <c r="AD13" s="59" t="n"/>
+      <c r="AE13" s="59" t="n"/>
+      <c r="AF13" s="60" t="n"/>
+      <c r="AG13" s="60" t="n"/>
+      <c r="AH13" s="60" t="n"/>
+    </row>
+    <row r="14" ht="4" customHeight="1">
+      <c r="A14" s="65" t="n"/>
+      <c r="B14" s="65" t="n"/>
+      <c r="C14" s="65" t="n"/>
+      <c r="D14" s="65" t="n"/>
+      <c r="E14" s="65" t="n"/>
+      <c r="F14" s="65" t="n"/>
+      <c r="G14" s="65" t="n"/>
+      <c r="H14" s="65" t="n"/>
+      <c r="I14" s="65" t="n"/>
+      <c r="J14" s="65" t="n"/>
+      <c r="K14" s="65" t="n"/>
+      <c r="L14" s="65" t="n"/>
+      <c r="M14" s="65" t="n"/>
+      <c r="N14" s="65" t="n"/>
+      <c r="O14" s="65" t="n"/>
+      <c r="P14" s="65" t="n"/>
+      <c r="Q14" s="65" t="n"/>
+      <c r="R14" s="65" t="n"/>
+      <c r="S14" s="65" t="n"/>
+      <c r="T14" s="65" t="n"/>
+      <c r="U14" s="65" t="n"/>
+      <c r="V14" s="65" t="n"/>
+      <c r="W14" s="65" t="n"/>
+      <c r="X14" s="65" t="n"/>
+      <c r="Y14" s="65" t="n"/>
+      <c r="Z14" s="65" t="n"/>
+      <c r="AA14" s="65" t="n"/>
+      <c r="AB14" s="65" t="n"/>
+      <c r="AC14" s="65" t="n"/>
+      <c r="AD14" s="65" t="n"/>
+      <c r="AE14" s="65" t="n"/>
+      <c r="AF14" s="65" t="n"/>
+      <c r="AG14" s="65" t="n"/>
+      <c r="AH14" s="65" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="67" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B15" s="54" t="inlineStr">
+        <is>
+          <t>Audit 日誌模型 + API #12-13</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D15" s="56" t="inlineStr">
+        <is>
+          <t>後端C</t>
+        </is>
+      </c>
+      <c r="E15" s="56" t="inlineStr">
+        <is>
+          <t>5/23</t>
+        </is>
+      </c>
+      <c r="F15" s="56" t="inlineStr">
+        <is>
+          <t>6/3</t>
+        </is>
+      </c>
+      <c r="G15" s="62" t="n"/>
+      <c r="H15" s="62" t="n"/>
+      <c r="I15" s="62" t="n"/>
+      <c r="J15" s="59" t="n"/>
+      <c r="K15" s="59" t="n"/>
+      <c r="L15" s="59" t="n"/>
+      <c r="M15" s="57" t="n"/>
+      <c r="N15" s="57" t="n"/>
+      <c r="O15" s="60" t="n"/>
+      <c r="P15" s="68" t="n"/>
+      <c r="Q15" s="60" t="n"/>
+      <c r="R15" s="60" t="n"/>
+      <c r="S15" s="61" t="n"/>
+      <c r="T15" s="61" t="n"/>
+      <c r="U15" s="61" t="n"/>
+      <c r="V15" s="61" t="n"/>
+      <c r="W15" s="62" t="n"/>
+      <c r="X15" s="62" t="n"/>
+      <c r="Y15" s="62" t="n"/>
+      <c r="Z15" s="62" t="n"/>
+      <c r="AA15" s="62" t="n"/>
+      <c r="AB15" s="59" t="n"/>
+      <c r="AC15" s="59" t="n"/>
+      <c r="AD15" s="59" t="n"/>
+      <c r="AE15" s="59" t="n"/>
+      <c r="AF15" s="60" t="n"/>
+      <c r="AG15" s="60" t="n"/>
+      <c r="AH15" s="60" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B16" s="54" t="inlineStr">
+        <is>
+          <t>Security Middleware 啟用 #11</t>
+        </is>
+      </c>
+      <c r="C16" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D16" s="56" t="inlineStr">
+        <is>
+          <t>後端C</t>
+        </is>
+      </c>
+      <c r="E16" s="56" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="F16" s="56" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+      <c r="G16" s="62" t="n"/>
+      <c r="H16" s="62" t="n"/>
+      <c r="I16" s="62" t="n"/>
+      <c r="J16" s="59" t="n"/>
+      <c r="K16" s="59" t="n"/>
+      <c r="L16" s="59" t="n"/>
+      <c r="M16" s="59" t="n"/>
+      <c r="N16" s="59" t="n"/>
+      <c r="O16" s="70" t="n"/>
+      <c r="P16" s="71" t="n"/>
+      <c r="Q16" s="60" t="n"/>
+      <c r="R16" s="60" t="n"/>
+      <c r="S16" s="61" t="n"/>
+      <c r="T16" s="61" t="n"/>
+      <c r="U16" s="61" t="n"/>
+      <c r="V16" s="61" t="n"/>
+      <c r="W16" s="62" t="n"/>
+      <c r="X16" s="62" t="n"/>
+      <c r="Y16" s="62" t="n"/>
+      <c r="Z16" s="62" t="n"/>
+      <c r="AA16" s="62" t="n"/>
+      <c r="AB16" s="59" t="n"/>
+      <c r="AC16" s="59" t="n"/>
+      <c r="AD16" s="59" t="n"/>
+      <c r="AE16" s="59" t="n"/>
+      <c r="AF16" s="60" t="n"/>
+      <c r="AG16" s="60" t="n"/>
+      <c r="AH16" s="60" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B17" s="54" t="inlineStr">
+        <is>
+          <t>P0 全量驗收補完</t>
+        </is>
+      </c>
+      <c r="C17" s="55" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E17" s="56" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
+      <c r="F17" s="56" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+      <c r="G17" s="62" t="n"/>
+      <c r="H17" s="62" t="n"/>
+      <c r="I17" s="62" t="n"/>
+      <c r="J17" s="59" t="n"/>
+      <c r="K17" s="59" t="n"/>
+      <c r="L17" s="59" t="n"/>
+      <c r="M17" s="59" t="n"/>
+      <c r="N17" s="59" t="n"/>
+      <c r="O17" s="57" t="n"/>
+      <c r="P17" s="64" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="Q17" s="60" t="n"/>
+      <c r="R17" s="60" t="n"/>
+      <c r="S17" s="61" t="n"/>
+      <c r="T17" s="61" t="n"/>
+      <c r="U17" s="61" t="n"/>
+      <c r="V17" s="61" t="n"/>
+      <c r="W17" s="62" t="n"/>
+      <c r="X17" s="62" t="n"/>
+      <c r="Y17" s="62" t="n"/>
+      <c r="Z17" s="62" t="n"/>
+      <c r="AA17" s="62" t="n"/>
+      <c r="AB17" s="59" t="n"/>
+      <c r="AC17" s="59" t="n"/>
+      <c r="AD17" s="59" t="n"/>
+      <c r="AE17" s="59" t="n"/>
+      <c r="AF17" s="60" t="n"/>
+      <c r="AG17" s="60" t="n"/>
+      <c r="AH17" s="60" t="n"/>
+    </row>
+    <row r="18" ht="4" customHeight="1">
+      <c r="A18" s="65" t="n"/>
+      <c r="B18" s="65" t="n"/>
+      <c r="C18" s="65" t="n"/>
+      <c r="D18" s="65" t="n"/>
+      <c r="E18" s="65" t="n"/>
+      <c r="F18" s="65" t="n"/>
+      <c r="G18" s="65" t="n"/>
+      <c r="H18" s="65" t="n"/>
+      <c r="I18" s="65" t="n"/>
+      <c r="J18" s="65" t="n"/>
+      <c r="K18" s="65" t="n"/>
+      <c r="L18" s="65" t="n"/>
+      <c r="M18" s="65" t="n"/>
+      <c r="N18" s="65" t="n"/>
+      <c r="O18" s="65" t="n"/>
+      <c r="P18" s="65" t="n"/>
+      <c r="Q18" s="65" t="n"/>
+      <c r="R18" s="65" t="n"/>
+      <c r="S18" s="65" t="n"/>
+      <c r="T18" s="65" t="n"/>
+      <c r="U18" s="65" t="n"/>
+      <c r="V18" s="65" t="n"/>
+      <c r="W18" s="65" t="n"/>
+      <c r="X18" s="65" t="n"/>
+      <c r="Y18" s="65" t="n"/>
+      <c r="Z18" s="65" t="n"/>
+      <c r="AA18" s="65" t="n"/>
+      <c r="AB18" s="65" t="n"/>
+      <c r="AC18" s="65" t="n"/>
+      <c r="AD18" s="65" t="n"/>
+      <c r="AE18" s="65" t="n"/>
+      <c r="AF18" s="65" t="n"/>
+      <c r="AG18" s="65" t="n"/>
+      <c r="AH18" s="65" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B19" s="54" t="inlineStr">
+        <is>
+          <t>Finance P1 #33-37</t>
+        </is>
+      </c>
+      <c r="C19" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t>後端B</t>
+        </is>
+      </c>
+      <c r="E19" s="56" t="inlineStr">
+        <is>
+          <t>6/20</t>
+        </is>
+      </c>
+      <c r="F19" s="56" t="inlineStr">
+        <is>
+          <t>7/1</t>
+        </is>
+      </c>
+      <c r="G19" s="62" t="n"/>
+      <c r="H19" s="62" t="n"/>
+      <c r="I19" s="62" t="n"/>
+      <c r="J19" s="59" t="n"/>
+      <c r="K19" s="59" t="n"/>
+      <c r="L19" s="59" t="n"/>
+      <c r="M19" s="59" t="n"/>
+      <c r="N19" s="59" t="n"/>
+      <c r="O19" s="60" t="n"/>
+      <c r="P19" s="60" t="n"/>
+      <c r="Q19" s="70" t="n"/>
+      <c r="R19" s="70" t="n"/>
+      <c r="S19" s="72" t="n"/>
+      <c r="T19" s="61" t="n"/>
+      <c r="U19" s="61" t="n"/>
+      <c r="V19" s="61" t="n"/>
+      <c r="W19" s="62" t="n"/>
+      <c r="X19" s="62" t="n"/>
+      <c r="Y19" s="62" t="n"/>
+      <c r="Z19" s="62" t="n"/>
+      <c r="AA19" s="62" t="n"/>
+      <c r="AB19" s="59" t="n"/>
+      <c r="AC19" s="59" t="n"/>
+      <c r="AD19" s="59" t="n"/>
+      <c r="AE19" s="59" t="n"/>
+      <c r="AF19" s="60" t="n"/>
+      <c r="AG19" s="60" t="n"/>
+      <c r="AH19" s="60" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="67" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="inlineStr">
+        <is>
+          <t>Members P1 #23-26</t>
+        </is>
+      </c>
+      <c r="C20" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D20" s="56" t="inlineStr">
+        <is>
+          <t>後端A</t>
+        </is>
+      </c>
+      <c r="E20" s="56" t="inlineStr">
+        <is>
+          <t>6/20</t>
+        </is>
+      </c>
+      <c r="F20" s="56" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="G20" s="62" t="n"/>
+      <c r="H20" s="62" t="n"/>
+      <c r="I20" s="62" t="n"/>
+      <c r="J20" s="59" t="n"/>
+      <c r="K20" s="59" t="n"/>
+      <c r="L20" s="59" t="n"/>
+      <c r="M20" s="59" t="n"/>
+      <c r="N20" s="59" t="n"/>
+      <c r="O20" s="60" t="n"/>
+      <c r="P20" s="60" t="n"/>
+      <c r="Q20" s="70" t="n"/>
+      <c r="R20" s="70" t="n"/>
+      <c r="S20" s="71" t="n"/>
+      <c r="T20" s="61" t="n"/>
+      <c r="U20" s="61" t="n"/>
+      <c r="V20" s="61" t="n"/>
+      <c r="W20" s="62" t="n"/>
+      <c r="X20" s="62" t="n"/>
+      <c r="Y20" s="62" t="n"/>
+      <c r="Z20" s="62" t="n"/>
+      <c r="AA20" s="62" t="n"/>
+      <c r="AB20" s="59" t="n"/>
+      <c r="AC20" s="59" t="n"/>
+      <c r="AD20" s="59" t="n"/>
+      <c r="AE20" s="59" t="n"/>
+      <c r="AF20" s="60" t="n"/>
+      <c r="AG20" s="60" t="n"/>
+      <c r="AH20" s="60" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B21" s="54" t="inlineStr">
+        <is>
+          <t>Operators P1 #18-19</t>
+        </is>
+      </c>
+      <c r="C21" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D21" s="56" t="inlineStr">
+        <is>
+          <t>後端A</t>
+        </is>
+      </c>
+      <c r="E21" s="56" t="inlineStr">
+        <is>
+          <t>6/20</t>
+        </is>
+      </c>
+      <c r="F21" s="56" t="inlineStr">
+        <is>
+          <t>7/1</t>
+        </is>
+      </c>
+      <c r="G21" s="62" t="n"/>
+      <c r="H21" s="62" t="n"/>
+      <c r="I21" s="62" t="n"/>
+      <c r="J21" s="59" t="n"/>
+      <c r="K21" s="59" t="n"/>
+      <c r="L21" s="59" t="n"/>
+      <c r="M21" s="59" t="n"/>
+      <c r="N21" s="59" t="n"/>
+      <c r="O21" s="60" t="n"/>
+      <c r="P21" s="60" t="n"/>
+      <c r="Q21" s="70" t="n"/>
+      <c r="R21" s="70" t="n"/>
+      <c r="S21" s="72" t="n"/>
+      <c r="T21" s="61" t="n"/>
+      <c r="U21" s="61" t="n"/>
+      <c r="V21" s="61" t="n"/>
+      <c r="W21" s="62" t="n"/>
+      <c r="X21" s="62" t="n"/>
+      <c r="Y21" s="62" t="n"/>
+      <c r="Z21" s="62" t="n"/>
+      <c r="AA21" s="62" t="n"/>
+      <c r="AB21" s="59" t="n"/>
+      <c r="AC21" s="59" t="n"/>
+      <c r="AD21" s="59" t="n"/>
+      <c r="AE21" s="59" t="n"/>
+      <c r="AF21" s="60" t="n"/>
+      <c r="AG21" s="60" t="n"/>
+      <c r="AH21" s="60" t="n"/>
+    </row>
+    <row r="22" ht="4" customHeight="1">
+      <c r="A22" s="65" t="n"/>
+      <c r="B22" s="65" t="n"/>
+      <c r="C22" s="65" t="n"/>
+      <c r="D22" s="65" t="n"/>
+      <c r="E22" s="65" t="n"/>
+      <c r="F22" s="65" t="n"/>
+      <c r="G22" s="65" t="n"/>
+      <c r="H22" s="65" t="n"/>
+      <c r="I22" s="65" t="n"/>
+      <c r="J22" s="65" t="n"/>
+      <c r="K22" s="65" t="n"/>
+      <c r="L22" s="65" t="n"/>
+      <c r="M22" s="65" t="n"/>
+      <c r="N22" s="65" t="n"/>
+      <c r="O22" s="65" t="n"/>
+      <c r="P22" s="65" t="n"/>
+      <c r="Q22" s="65" t="n"/>
+      <c r="R22" s="65" t="n"/>
+      <c r="S22" s="65" t="n"/>
+      <c r="T22" s="65" t="n"/>
+      <c r="U22" s="65" t="n"/>
+      <c r="V22" s="65" t="n"/>
+      <c r="W22" s="65" t="n"/>
+      <c r="X22" s="65" t="n"/>
+      <c r="Y22" s="65" t="n"/>
+      <c r="Z22" s="65" t="n"/>
+      <c r="AA22" s="65" t="n"/>
+      <c r="AB22" s="65" t="n"/>
+      <c r="AC22" s="65" t="n"/>
+      <c r="AD22" s="65" t="n"/>
+      <c r="AE22" s="65" t="n"/>
+      <c r="AF22" s="65" t="n"/>
+      <c r="AG22" s="65" t="n"/>
+      <c r="AH22" s="65" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="73" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B23" s="54" t="inlineStr">
+        <is>
+          <t>Queue / Export #14-15</t>
+        </is>
+      </c>
+      <c r="C23" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D23" s="56" t="inlineStr">
+        <is>
+          <t>後端B</t>
+        </is>
+      </c>
+      <c r="E23" s="56" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+      <c r="F23" s="56" t="inlineStr">
+        <is>
+          <t>7/22</t>
+        </is>
+      </c>
+      <c r="G23" s="62" t="n"/>
+      <c r="H23" s="62" t="n"/>
+      <c r="I23" s="62" t="n"/>
+      <c r="J23" s="59" t="n"/>
+      <c r="K23" s="59" t="n"/>
+      <c r="L23" s="59" t="n"/>
+      <c r="M23" s="59" t="n"/>
+      <c r="N23" s="59" t="n"/>
+      <c r="O23" s="60" t="n"/>
+      <c r="P23" s="60" t="n"/>
+      <c r="Q23" s="60" t="n"/>
+      <c r="R23" s="60" t="n"/>
+      <c r="S23" s="61" t="n"/>
+      <c r="T23" s="70" t="n"/>
+      <c r="U23" s="70" t="n"/>
+      <c r="V23" s="61" t="n"/>
+      <c r="W23" s="58" t="n"/>
+      <c r="X23" s="62" t="n"/>
+      <c r="Y23" s="62" t="n"/>
+      <c r="Z23" s="62" t="n"/>
+      <c r="AA23" s="62" t="n"/>
+      <c r="AB23" s="59" t="n"/>
+      <c r="AC23" s="59" t="n"/>
+      <c r="AD23" s="59" t="n"/>
+      <c r="AE23" s="59" t="n"/>
+      <c r="AF23" s="60" t="n"/>
+      <c r="AG23" s="60" t="n"/>
+      <c r="AH23" s="60" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="73" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B24" s="54" t="inlineStr">
+        <is>
+          <t>System Settings #38-40</t>
+        </is>
+      </c>
+      <c r="C24" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D24" s="56" t="inlineStr">
+        <is>
+          <t>後端C</t>
+        </is>
+      </c>
+      <c r="E24" s="56" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+      <c r="F24" s="56" t="inlineStr">
+        <is>
+          <t>7/22</t>
+        </is>
+      </c>
+      <c r="G24" s="62" t="n"/>
+      <c r="H24" s="62" t="n"/>
+      <c r="I24" s="62" t="n"/>
+      <c r="J24" s="59" t="n"/>
+      <c r="K24" s="59" t="n"/>
+      <c r="L24" s="59" t="n"/>
+      <c r="M24" s="59" t="n"/>
+      <c r="N24" s="59" t="n"/>
+      <c r="O24" s="60" t="n"/>
+      <c r="P24" s="60" t="n"/>
+      <c r="Q24" s="60" t="n"/>
+      <c r="R24" s="60" t="n"/>
+      <c r="S24" s="61" t="n"/>
+      <c r="T24" s="70" t="n"/>
+      <c r="U24" s="70" t="n"/>
+      <c r="V24" s="61" t="n"/>
+      <c r="W24" s="58" t="n"/>
+      <c r="X24" s="62" t="n"/>
+      <c r="Y24" s="62" t="n"/>
+      <c r="Z24" s="62" t="n"/>
+      <c r="AA24" s="62" t="n"/>
+      <c r="AB24" s="59" t="n"/>
+      <c r="AC24" s="59" t="n"/>
+      <c r="AD24" s="59" t="n"/>
+      <c r="AE24" s="59" t="n"/>
+      <c r="AF24" s="60" t="n"/>
+      <c r="AG24" s="60" t="n"/>
+      <c r="AH24" s="60" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="73" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B25" s="54" t="inlineStr">
+        <is>
+          <t>Messages #41-43</t>
+        </is>
+      </c>
+      <c r="C25" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D25" s="56" t="inlineStr">
+        <is>
+          <t>後端C</t>
+        </is>
+      </c>
+      <c r="E25" s="56" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+      <c r="F25" s="56" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+      <c r="G25" s="62" t="n"/>
+      <c r="H25" s="62" t="n"/>
+      <c r="I25" s="62" t="n"/>
+      <c r="J25" s="59" t="n"/>
+      <c r="K25" s="59" t="n"/>
+      <c r="L25" s="59" t="n"/>
+      <c r="M25" s="59" t="n"/>
+      <c r="N25" s="59" t="n"/>
+      <c r="O25" s="60" t="n"/>
+      <c r="P25" s="60" t="n"/>
+      <c r="Q25" s="60" t="n"/>
+      <c r="R25" s="60" t="n"/>
+      <c r="S25" s="61" t="n"/>
+      <c r="T25" s="61" t="n"/>
+      <c r="U25" s="70" t="n"/>
+      <c r="V25" s="70" t="n"/>
+      <c r="W25" s="58" t="n"/>
+      <c r="X25" s="62" t="n"/>
+      <c r="Y25" s="62" t="n"/>
+      <c r="Z25" s="62" t="n"/>
+      <c r="AA25" s="62" t="n"/>
+      <c r="AB25" s="59" t="n"/>
+      <c r="AC25" s="59" t="n"/>
+      <c r="AD25" s="59" t="n"/>
+      <c r="AE25" s="59" t="n"/>
+      <c r="AF25" s="60" t="n"/>
+      <c r="AG25" s="60" t="n"/>
+      <c r="AH25" s="60" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="73" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B26" s="54" t="inlineStr">
+        <is>
+          <t>Agents #44-47</t>
+        </is>
+      </c>
+      <c r="C26" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D26" s="56" t="inlineStr">
+        <is>
+          <t>後端A</t>
+        </is>
+      </c>
+      <c r="E26" s="56" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+      <c r="F26" s="56" t="inlineStr">
+        <is>
+          <t>8/5</t>
+        </is>
+      </c>
+      <c r="G26" s="62" t="n"/>
+      <c r="H26" s="62" t="n"/>
+      <c r="I26" s="62" t="n"/>
+      <c r="J26" s="59" t="n"/>
+      <c r="K26" s="59" t="n"/>
+      <c r="L26" s="59" t="n"/>
+      <c r="M26" s="59" t="n"/>
+      <c r="N26" s="59" t="n"/>
+      <c r="O26" s="60" t="n"/>
+      <c r="P26" s="60" t="n"/>
+      <c r="Q26" s="60" t="n"/>
+      <c r="R26" s="60" t="n"/>
+      <c r="S26" s="61" t="n"/>
+      <c r="T26" s="70" t="n"/>
+      <c r="U26" s="70" t="n"/>
+      <c r="V26" s="70" t="n"/>
+      <c r="W26" s="74" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="X26" s="62" t="n"/>
+      <c r="Y26" s="62" t="n"/>
+      <c r="Z26" s="62" t="n"/>
+      <c r="AA26" s="62" t="n"/>
+      <c r="AB26" s="59" t="n"/>
+      <c r="AC26" s="59" t="n"/>
+      <c r="AD26" s="59" t="n"/>
+      <c r="AE26" s="59" t="n"/>
+      <c r="AF26" s="60" t="n"/>
+      <c r="AG26" s="60" t="n"/>
+      <c r="AH26" s="60" t="n"/>
+    </row>
+    <row r="27" ht="4" customHeight="1">
+      <c r="A27" s="65" t="n"/>
+      <c r="B27" s="65" t="n"/>
+      <c r="C27" s="65" t="n"/>
+      <c r="D27" s="65" t="n"/>
+      <c r="E27" s="65" t="n"/>
+      <c r="F27" s="65" t="n"/>
+      <c r="G27" s="65" t="n"/>
+      <c r="H27" s="65" t="n"/>
+      <c r="I27" s="65" t="n"/>
+      <c r="J27" s="65" t="n"/>
+      <c r="K27" s="65" t="n"/>
+      <c r="L27" s="65" t="n"/>
+      <c r="M27" s="65" t="n"/>
+      <c r="N27" s="65" t="n"/>
+      <c r="O27" s="65" t="n"/>
+      <c r="P27" s="65" t="n"/>
+      <c r="Q27" s="65" t="n"/>
+      <c r="R27" s="65" t="n"/>
+      <c r="S27" s="65" t="n"/>
+      <c r="T27" s="65" t="n"/>
+      <c r="U27" s="65" t="n"/>
+      <c r="V27" s="65" t="n"/>
+      <c r="W27" s="65" t="n"/>
+      <c r="X27" s="65" t="n"/>
+      <c r="Y27" s="65" t="n"/>
+      <c r="Z27" s="65" t="n"/>
+      <c r="AA27" s="65" t="n"/>
+      <c r="AB27" s="65" t="n"/>
+      <c r="AC27" s="65" t="n"/>
+      <c r="AD27" s="65" t="n"/>
+      <c r="AE27" s="65" t="n"/>
+      <c r="AF27" s="65" t="n"/>
+      <c r="AG27" s="65" t="n"/>
+      <c r="AH27" s="65" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="73" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B28" s="54" t="inlineStr">
+        <is>
+          <t>Games #48-51</t>
+        </is>
+      </c>
+      <c r="C28" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D28" s="56" t="inlineStr">
+        <is>
+          <t>後端D</t>
+        </is>
+      </c>
+      <c r="E28" s="56" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="F28" s="56" t="inlineStr">
+        <is>
+          <t>8/19</t>
+        </is>
+      </c>
+      <c r="G28" s="62" t="n"/>
+      <c r="H28" s="62" t="n"/>
+      <c r="I28" s="62" t="n"/>
+      <c r="J28" s="59" t="n"/>
+      <c r="K28" s="59" t="n"/>
+      <c r="L28" s="59" t="n"/>
+      <c r="M28" s="59" t="n"/>
+      <c r="N28" s="59" t="n"/>
+      <c r="O28" s="60" t="n"/>
+      <c r="P28" s="60" t="n"/>
+      <c r="Q28" s="60" t="n"/>
+      <c r="R28" s="60" t="n"/>
+      <c r="S28" s="61" t="n"/>
+      <c r="T28" s="61" t="n"/>
+      <c r="U28" s="61" t="n"/>
+      <c r="V28" s="61" t="n"/>
+      <c r="W28" s="62" t="n"/>
+      <c r="X28" s="70" t="n"/>
+      <c r="Y28" s="70" t="n"/>
+      <c r="Z28" s="62" t="n"/>
+      <c r="AA28" s="58" t="n"/>
+      <c r="AB28" s="59" t="n"/>
+      <c r="AC28" s="59" t="n"/>
+      <c r="AD28" s="59" t="n"/>
+      <c r="AE28" s="59" t="n"/>
+      <c r="AF28" s="60" t="n"/>
+      <c r="AG28" s="60" t="n"/>
+      <c r="AH28" s="60" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="73" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B29" s="54" t="inlineStr">
+        <is>
+          <t>Promotions #52-54</t>
+        </is>
+      </c>
+      <c r="C29" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D29" s="56" t="inlineStr">
+        <is>
+          <t>後端D</t>
+        </is>
+      </c>
+      <c r="E29" s="56" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+      <c r="F29" s="56" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="G29" s="62" t="n"/>
+      <c r="H29" s="62" t="n"/>
+      <c r="I29" s="62" t="n"/>
+      <c r="J29" s="59" t="n"/>
+      <c r="K29" s="59" t="n"/>
+      <c r="L29" s="59" t="n"/>
+      <c r="M29" s="59" t="n"/>
+      <c r="N29" s="59" t="n"/>
+      <c r="O29" s="60" t="n"/>
+      <c r="P29" s="60" t="n"/>
+      <c r="Q29" s="60" t="n"/>
+      <c r="R29" s="60" t="n"/>
+      <c r="S29" s="61" t="n"/>
+      <c r="T29" s="61" t="n"/>
+      <c r="U29" s="61" t="n"/>
+      <c r="V29" s="61" t="n"/>
+      <c r="W29" s="62" t="n"/>
+      <c r="X29" s="62" t="n"/>
+      <c r="Y29" s="70" t="n"/>
+      <c r="Z29" s="70" t="n"/>
+      <c r="AA29" s="58" t="n"/>
+      <c r="AB29" s="59" t="n"/>
+      <c r="AC29" s="59" t="n"/>
+      <c r="AD29" s="59" t="n"/>
+      <c r="AE29" s="59" t="n"/>
+      <c r="AF29" s="60" t="n"/>
+      <c r="AG29" s="60" t="n"/>
+      <c r="AH29" s="60" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="73" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B30" s="54" t="inlineStr">
+        <is>
+          <t>Reports #55-56</t>
+        </is>
+      </c>
+      <c r="C30" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D30" s="56" t="inlineStr">
+        <is>
+          <t>後端D</t>
+        </is>
+      </c>
+      <c r="E30" s="56" t="inlineStr">
+        <is>
+          <t>8/22</t>
+        </is>
+      </c>
+      <c r="F30" s="56" t="inlineStr">
+        <is>
+          <t>9/2</t>
+        </is>
+      </c>
+      <c r="G30" s="62" t="n"/>
+      <c r="H30" s="62" t="n"/>
+      <c r="I30" s="62" t="n"/>
+      <c r="J30" s="59" t="n"/>
+      <c r="K30" s="59" t="n"/>
+      <c r="L30" s="59" t="n"/>
+      <c r="M30" s="59" t="n"/>
+      <c r="N30" s="59" t="n"/>
+      <c r="O30" s="60" t="n"/>
+      <c r="P30" s="60" t="n"/>
+      <c r="Q30" s="60" t="n"/>
+      <c r="R30" s="60" t="n"/>
+      <c r="S30" s="61" t="n"/>
+      <c r="T30" s="61" t="n"/>
+      <c r="U30" s="61" t="n"/>
+      <c r="V30" s="61" t="n"/>
+      <c r="W30" s="62" t="n"/>
+      <c r="X30" s="62" t="n"/>
+      <c r="Y30" s="62" t="n"/>
+      <c r="Z30" s="70" t="n"/>
+      <c r="AA30" s="71" t="n"/>
+      <c r="AB30" s="59" t="n"/>
+      <c r="AC30" s="59" t="n"/>
+      <c r="AD30" s="59" t="n"/>
+      <c r="AE30" s="59" t="n"/>
+      <c r="AF30" s="60" t="n"/>
+      <c r="AG30" s="60" t="n"/>
+      <c r="AH30" s="60" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="73" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B31" s="54" t="inlineStr">
+        <is>
+          <t>Integration P1 #65-66</t>
+        </is>
+      </c>
+      <c r="C31" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D31" s="56" t="inlineStr">
+        <is>
+          <t>後端B</t>
+        </is>
+      </c>
+      <c r="E31" s="56" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="F31" s="56" t="inlineStr">
+        <is>
+          <t>9/2</t>
+        </is>
+      </c>
+      <c r="G31" s="62" t="n"/>
+      <c r="H31" s="62" t="n"/>
+      <c r="I31" s="62" t="n"/>
+      <c r="J31" s="59" t="n"/>
+      <c r="K31" s="59" t="n"/>
+      <c r="L31" s="59" t="n"/>
+      <c r="M31" s="59" t="n"/>
+      <c r="N31" s="59" t="n"/>
+      <c r="O31" s="60" t="n"/>
+      <c r="P31" s="60" t="n"/>
+      <c r="Q31" s="60" t="n"/>
+      <c r="R31" s="60" t="n"/>
+      <c r="S31" s="61" t="n"/>
+      <c r="T31" s="61" t="n"/>
+      <c r="U31" s="61" t="n"/>
+      <c r="V31" s="61" t="n"/>
+      <c r="W31" s="62" t="n"/>
+      <c r="X31" s="70" t="n"/>
+      <c r="Y31" s="70" t="n"/>
+      <c r="Z31" s="70" t="n"/>
+      <c r="AA31" s="74" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="AB31" s="59" t="n"/>
+      <c r="AC31" s="59" t="n"/>
+      <c r="AD31" s="59" t="n"/>
+      <c r="AE31" s="59" t="n"/>
+      <c r="AF31" s="60" t="n"/>
+      <c r="AG31" s="60" t="n"/>
+      <c r="AH31" s="60" t="n"/>
+    </row>
+    <row r="32" ht="4" customHeight="1">
+      <c r="A32" s="65" t="n"/>
+      <c r="B32" s="65" t="n"/>
+      <c r="C32" s="65" t="n"/>
+      <c r="D32" s="65" t="n"/>
+      <c r="E32" s="65" t="n"/>
+      <c r="F32" s="65" t="n"/>
+      <c r="G32" s="65" t="n"/>
+      <c r="H32" s="65" t="n"/>
+      <c r="I32" s="65" t="n"/>
+      <c r="J32" s="65" t="n"/>
+      <c r="K32" s="65" t="n"/>
+      <c r="L32" s="65" t="n"/>
+      <c r="M32" s="65" t="n"/>
+      <c r="N32" s="65" t="n"/>
+      <c r="O32" s="65" t="n"/>
+      <c r="P32" s="65" t="n"/>
+      <c r="Q32" s="65" t="n"/>
+      <c r="R32" s="65" t="n"/>
+      <c r="S32" s="65" t="n"/>
+      <c r="T32" s="65" t="n"/>
+      <c r="U32" s="65" t="n"/>
+      <c r="V32" s="65" t="n"/>
+      <c r="W32" s="65" t="n"/>
+      <c r="X32" s="65" t="n"/>
+      <c r="Y32" s="65" t="n"/>
+      <c r="Z32" s="65" t="n"/>
+      <c r="AA32" s="65" t="n"/>
+      <c r="AB32" s="65" t="n"/>
+      <c r="AC32" s="65" t="n"/>
+      <c r="AD32" s="65" t="n"/>
+      <c r="AE32" s="65" t="n"/>
+      <c r="AF32" s="65" t="n"/>
+      <c r="AG32" s="65" t="n"/>
+      <c r="AH32" s="65" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="75" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="B33" s="54" t="inlineStr">
+        <is>
+          <t>測試覆蓋 #69</t>
+        </is>
+      </c>
+      <c r="C33" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D33" s="56" t="inlineStr">
+        <is>
+          <t>後端C</t>
+        </is>
+      </c>
+      <c r="E33" s="56" t="inlineStr">
+        <is>
+          <t>9/5</t>
+        </is>
+      </c>
+      <c r="F33" s="56" t="inlineStr">
+        <is>
+          <t>9/16</t>
+        </is>
+      </c>
+      <c r="G33" s="62" t="n"/>
+      <c r="H33" s="62" t="n"/>
+      <c r="I33" s="62" t="n"/>
+      <c r="J33" s="59" t="n"/>
+      <c r="K33" s="59" t="n"/>
+      <c r="L33" s="59" t="n"/>
+      <c r="M33" s="59" t="n"/>
+      <c r="N33" s="59" t="n"/>
+      <c r="O33" s="60" t="n"/>
+      <c r="P33" s="60" t="n"/>
+      <c r="Q33" s="60" t="n"/>
+      <c r="R33" s="60" t="n"/>
+      <c r="S33" s="61" t="n"/>
+      <c r="T33" s="61" t="n"/>
+      <c r="U33" s="61" t="n"/>
+      <c r="V33" s="61" t="n"/>
+      <c r="W33" s="62" t="n"/>
+      <c r="X33" s="62" t="n"/>
+      <c r="Y33" s="62" t="n"/>
+      <c r="Z33" s="62" t="n"/>
+      <c r="AA33" s="62" t="n"/>
+      <c r="AB33" s="70" t="n"/>
+      <c r="AC33" s="70" t="n"/>
+      <c r="AD33" s="66" t="n"/>
+      <c r="AE33" s="59" t="n"/>
+      <c r="AF33" s="60" t="n"/>
+      <c r="AG33" s="60" t="n"/>
+      <c r="AH33" s="60" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="75" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="B34" s="54" t="inlineStr">
+        <is>
+          <t>效能優化 + 監控 #70-71</t>
+        </is>
+      </c>
+      <c r="C34" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D34" s="56" t="inlineStr">
+        <is>
+          <t>後端C</t>
+        </is>
+      </c>
+      <c r="E34" s="56" t="inlineStr">
+        <is>
+          <t>9/5</t>
+        </is>
+      </c>
+      <c r="F34" s="56" t="inlineStr">
+        <is>
+          <t>9/16</t>
+        </is>
+      </c>
+      <c r="G34" s="62" t="n"/>
+      <c r="H34" s="62" t="n"/>
+      <c r="I34" s="62" t="n"/>
+      <c r="J34" s="59" t="n"/>
+      <c r="K34" s="59" t="n"/>
+      <c r="L34" s="59" t="n"/>
+      <c r="M34" s="59" t="n"/>
+      <c r="N34" s="59" t="n"/>
+      <c r="O34" s="60" t="n"/>
+      <c r="P34" s="60" t="n"/>
+      <c r="Q34" s="60" t="n"/>
+      <c r="R34" s="60" t="n"/>
+      <c r="S34" s="61" t="n"/>
+      <c r="T34" s="61" t="n"/>
+      <c r="U34" s="61" t="n"/>
+      <c r="V34" s="61" t="n"/>
+      <c r="W34" s="62" t="n"/>
+      <c r="X34" s="62" t="n"/>
+      <c r="Y34" s="62" t="n"/>
+      <c r="Z34" s="62" t="n"/>
+      <c r="AA34" s="62" t="n"/>
+      <c r="AB34" s="70" t="n"/>
+      <c r="AC34" s="70" t="n"/>
+      <c r="AD34" s="66" t="n"/>
+      <c r="AE34" s="59" t="n"/>
+      <c r="AF34" s="60" t="n"/>
+      <c r="AG34" s="60" t="n"/>
+      <c r="AH34" s="60" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="75" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="B35" s="54" t="inlineStr">
+        <is>
+          <t>Dashboard APIs #24-29</t>
+        </is>
+      </c>
+      <c r="C35" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D35" s="56" t="inlineStr">
+        <is>
+          <t>後端D</t>
+        </is>
+      </c>
+      <c r="E35" s="56" t="inlineStr">
+        <is>
+          <t>9/5</t>
+        </is>
+      </c>
+      <c r="F35" s="56" t="inlineStr">
+        <is>
+          <t>9/23</t>
+        </is>
+      </c>
+      <c r="G35" s="62" t="n"/>
+      <c r="H35" s="62" t="n"/>
+      <c r="I35" s="62" t="n"/>
+      <c r="J35" s="59" t="n"/>
+      <c r="K35" s="59" t="n"/>
+      <c r="L35" s="59" t="n"/>
+      <c r="M35" s="59" t="n"/>
+      <c r="N35" s="59" t="n"/>
+      <c r="O35" s="60" t="n"/>
+      <c r="P35" s="60" t="n"/>
+      <c r="Q35" s="60" t="n"/>
+      <c r="R35" s="60" t="n"/>
+      <c r="S35" s="61" t="n"/>
+      <c r="T35" s="61" t="n"/>
+      <c r="U35" s="61" t="n"/>
+      <c r="V35" s="61" t="n"/>
+      <c r="W35" s="62" t="n"/>
+      <c r="X35" s="62" t="n"/>
+      <c r="Y35" s="62" t="n"/>
+      <c r="Z35" s="62" t="n"/>
+      <c r="AA35" s="62" t="n"/>
+      <c r="AB35" s="70" t="n"/>
+      <c r="AC35" s="70" t="n"/>
+      <c r="AD35" s="71" t="n"/>
+      <c r="AE35" s="59" t="n"/>
+      <c r="AF35" s="60" t="n"/>
+      <c r="AG35" s="60" t="n"/>
+      <c r="AH35" s="60" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="75" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="B36" s="54" t="inlineStr">
+        <is>
+          <t>文件與交接 #72</t>
+        </is>
+      </c>
+      <c r="C36" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D36" s="56" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E36" s="56" t="inlineStr">
+        <is>
+          <t>9/12</t>
+        </is>
+      </c>
+      <c r="F36" s="56" t="inlineStr">
+        <is>
+          <t>9/23</t>
+        </is>
+      </c>
+      <c r="G36" s="62" t="n"/>
+      <c r="H36" s="62" t="n"/>
+      <c r="I36" s="62" t="n"/>
+      <c r="J36" s="59" t="n"/>
+      <c r="K36" s="59" t="n"/>
+      <c r="L36" s="59" t="n"/>
+      <c r="M36" s="59" t="n"/>
+      <c r="N36" s="59" t="n"/>
+      <c r="O36" s="60" t="n"/>
+      <c r="P36" s="60" t="n"/>
+      <c r="Q36" s="60" t="n"/>
+      <c r="R36" s="60" t="n"/>
+      <c r="S36" s="61" t="n"/>
+      <c r="T36" s="61" t="n"/>
+      <c r="U36" s="61" t="n"/>
+      <c r="V36" s="61" t="n"/>
+      <c r="W36" s="62" t="n"/>
+      <c r="X36" s="62" t="n"/>
+      <c r="Y36" s="62" t="n"/>
+      <c r="Z36" s="62" t="n"/>
+      <c r="AA36" s="62" t="n"/>
+      <c r="AB36" s="59" t="n"/>
+      <c r="AC36" s="70" t="n"/>
+      <c r="AD36" s="74" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="AE36" s="59" t="n"/>
+      <c r="AF36" s="60" t="n"/>
+      <c r="AG36" s="60" t="n"/>
+      <c r="AH36" s="60" t="n"/>
+    </row>
+    <row r="37" ht="4" customHeight="1">
+      <c r="A37" s="65" t="n"/>
+      <c r="B37" s="65" t="n"/>
+      <c r="C37" s="65" t="n"/>
+      <c r="D37" s="65" t="n"/>
+      <c r="E37" s="65" t="n"/>
+      <c r="F37" s="65" t="n"/>
+      <c r="G37" s="65" t="n"/>
+      <c r="H37" s="65" t="n"/>
+      <c r="I37" s="65" t="n"/>
+      <c r="J37" s="65" t="n"/>
+      <c r="K37" s="65" t="n"/>
+      <c r="L37" s="65" t="n"/>
+      <c r="M37" s="65" t="n"/>
+      <c r="N37" s="65" t="n"/>
+      <c r="O37" s="65" t="n"/>
+      <c r="P37" s="65" t="n"/>
+      <c r="Q37" s="65" t="n"/>
+      <c r="R37" s="65" t="n"/>
+      <c r="S37" s="65" t="n"/>
+      <c r="T37" s="65" t="n"/>
+      <c r="U37" s="65" t="n"/>
+      <c r="V37" s="65" t="n"/>
+      <c r="W37" s="65" t="n"/>
+      <c r="X37" s="65" t="n"/>
+      <c r="Y37" s="65" t="n"/>
+      <c r="Z37" s="65" t="n"/>
+      <c r="AA37" s="65" t="n"/>
+      <c r="AB37" s="65" t="n"/>
+      <c r="AC37" s="65" t="n"/>
+      <c r="AD37" s="65" t="n"/>
+      <c r="AE37" s="65" t="n"/>
+      <c r="AF37" s="65" t="n"/>
+      <c r="AG37" s="65" t="n"/>
+      <c r="AH37" s="65" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="76" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="B38" s="54" t="inlineStr">
+        <is>
+          <t>Layout #57-59</t>
+        </is>
+      </c>
+      <c r="C38" s="77" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D38" s="56" t="inlineStr">
+        <is>
+          <t>後端D</t>
+        </is>
+      </c>
+      <c r="E38" s="56" t="inlineStr">
+        <is>
+          <t>9/26</t>
+        </is>
+      </c>
+      <c r="F38" s="56" t="inlineStr">
+        <is>
+          <t>10/7</t>
+        </is>
+      </c>
+      <c r="G38" s="62" t="n"/>
+      <c r="H38" s="62" t="n"/>
+      <c r="I38" s="62" t="n"/>
+      <c r="J38" s="59" t="n"/>
+      <c r="K38" s="59" t="n"/>
+      <c r="L38" s="59" t="n"/>
+      <c r="M38" s="59" t="n"/>
+      <c r="N38" s="59" t="n"/>
+      <c r="O38" s="60" t="n"/>
+      <c r="P38" s="60" t="n"/>
+      <c r="Q38" s="60" t="n"/>
+      <c r="R38" s="60" t="n"/>
+      <c r="S38" s="61" t="n"/>
+      <c r="T38" s="61" t="n"/>
+      <c r="U38" s="61" t="n"/>
+      <c r="V38" s="61" t="n"/>
+      <c r="W38" s="62" t="n"/>
+      <c r="X38" s="62" t="n"/>
+      <c r="Y38" s="62" t="n"/>
+      <c r="Z38" s="62" t="n"/>
+      <c r="AA38" s="62" t="n"/>
+      <c r="AB38" s="59" t="n"/>
+      <c r="AC38" s="59" t="n"/>
+      <c r="AD38" s="59" t="n"/>
+      <c r="AE38" s="78" t="n"/>
+      <c r="AF38" s="78" t="n"/>
+      <c r="AG38" s="60" t="n"/>
+      <c r="AH38" s="68" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="76" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="B39" s="54" t="inlineStr">
+        <is>
+          <t>Official 官網 #60-61</t>
+        </is>
+      </c>
+      <c r="C39" s="77" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D39" s="56" t="inlineStr">
+        <is>
+          <t>後端D</t>
+        </is>
+      </c>
+      <c r="E39" s="56" t="inlineStr">
+        <is>
+          <t>10/3</t>
+        </is>
+      </c>
+      <c r="F39" s="56" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+      <c r="G39" s="62" t="n"/>
+      <c r="H39" s="62" t="n"/>
+      <c r="I39" s="62" t="n"/>
+      <c r="J39" s="59" t="n"/>
+      <c r="K39" s="59" t="n"/>
+      <c r="L39" s="59" t="n"/>
+      <c r="M39" s="59" t="n"/>
+      <c r="N39" s="59" t="n"/>
+      <c r="O39" s="60" t="n"/>
+      <c r="P39" s="60" t="n"/>
+      <c r="Q39" s="60" t="n"/>
+      <c r="R39" s="60" t="n"/>
+      <c r="S39" s="61" t="n"/>
+      <c r="T39" s="61" t="n"/>
+      <c r="U39" s="61" t="n"/>
+      <c r="V39" s="61" t="n"/>
+      <c r="W39" s="62" t="n"/>
+      <c r="X39" s="62" t="n"/>
+      <c r="Y39" s="62" t="n"/>
+      <c r="Z39" s="62" t="n"/>
+      <c r="AA39" s="62" t="n"/>
+      <c r="AB39" s="59" t="n"/>
+      <c r="AC39" s="59" t="n"/>
+      <c r="AD39" s="59" t="n"/>
+      <c r="AE39" s="59" t="n"/>
+      <c r="AF39" s="78" t="n"/>
+      <c r="AG39" s="78" t="n"/>
+      <c r="AH39" s="68" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="76" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="B40" s="54" t="inlineStr">
+        <is>
+          <t>Payments #62-64</t>
+        </is>
+      </c>
+      <c r="C40" s="77" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D40" s="56" t="inlineStr">
+        <is>
+          <t>後端B</t>
+        </is>
+      </c>
+      <c r="E40" s="56" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="F40" s="56" t="inlineStr">
+        <is>
+          <t>10/21</t>
+        </is>
+      </c>
+      <c r="G40" s="62" t="n"/>
+      <c r="H40" s="62" t="n"/>
+      <c r="I40" s="62" t="n"/>
+      <c r="J40" s="59" t="n"/>
+      <c r="K40" s="59" t="n"/>
+      <c r="L40" s="59" t="n"/>
+      <c r="M40" s="59" t="n"/>
+      <c r="N40" s="59" t="n"/>
+      <c r="O40" s="60" t="n"/>
+      <c r="P40" s="60" t="n"/>
+      <c r="Q40" s="60" t="n"/>
+      <c r="R40" s="60" t="n"/>
+      <c r="S40" s="61" t="n"/>
+      <c r="T40" s="61" t="n"/>
+      <c r="U40" s="61" t="n"/>
+      <c r="V40" s="61" t="n"/>
+      <c r="W40" s="62" t="n"/>
+      <c r="X40" s="62" t="n"/>
+      <c r="Y40" s="62" t="n"/>
+      <c r="Z40" s="62" t="n"/>
+      <c r="AA40" s="62" t="n"/>
+      <c r="AB40" s="59" t="n"/>
+      <c r="AC40" s="59" t="n"/>
+      <c r="AD40" s="59" t="n"/>
+      <c r="AE40" s="59" t="n"/>
+      <c r="AF40" s="60" t="n"/>
+      <c r="AG40" s="78" t="n"/>
+      <c r="AH40" s="79" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="76" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="B41" s="54" t="inlineStr">
+        <is>
+          <t>Integration P2 #67-68</t>
+        </is>
+      </c>
+      <c r="C41" s="77" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D41" s="56" t="inlineStr">
+        <is>
+          <t>後端B</t>
+        </is>
+      </c>
+      <c r="E41" s="56" t="inlineStr">
+        <is>
+          <t>9/26</t>
+        </is>
+      </c>
+      <c r="F41" s="56" t="inlineStr">
+        <is>
+          <t>10/21</t>
+        </is>
+      </c>
+      <c r="G41" s="62" t="n"/>
+      <c r="H41" s="62" t="n"/>
+      <c r="I41" s="62" t="n"/>
+      <c r="J41" s="59" t="n"/>
+      <c r="K41" s="59" t="n"/>
+      <c r="L41" s="59" t="n"/>
+      <c r="M41" s="59" t="n"/>
+      <c r="N41" s="59" t="n"/>
+      <c r="O41" s="60" t="n"/>
+      <c r="P41" s="60" t="n"/>
+      <c r="Q41" s="60" t="n"/>
+      <c r="R41" s="60" t="n"/>
+      <c r="S41" s="61" t="n"/>
+      <c r="T41" s="61" t="n"/>
+      <c r="U41" s="61" t="n"/>
+      <c r="V41" s="61" t="n"/>
+      <c r="W41" s="62" t="n"/>
+      <c r="X41" s="62" t="n"/>
+      <c r="Y41" s="62" t="n"/>
+      <c r="Z41" s="62" t="n"/>
+      <c r="AA41" s="62" t="n"/>
+      <c r="AB41" s="59" t="n"/>
+      <c r="AC41" s="59" t="n"/>
+      <c r="AD41" s="59" t="n"/>
+      <c r="AE41" s="78" t="n"/>
+      <c r="AF41" s="78" t="n"/>
+      <c r="AG41" s="78" t="n"/>
+      <c r="AH41" s="80" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="81" t="inlineStr">
+        <is>
+          <t>里程碑截止日 ▼</t>
+        </is>
+      </c>
+      <c r="G43" s="37" t="n"/>
+      <c r="H43" s="37" t="n"/>
+      <c r="I43" s="82" t="inlineStr">
+        <is>
+          <t>M1
+P0 可串接</t>
+        </is>
+      </c>
+      <c r="J43" s="39" t="n"/>
+      <c r="K43" s="39" t="n"/>
+      <c r="L43" s="82" t="inlineStr">
+        <is>
+          <t>M2
+財務核心</t>
+        </is>
+      </c>
+      <c r="M43" s="39" t="n"/>
+      <c r="N43" s="39" t="n"/>
+      <c r="O43" s="41" t="n"/>
+      <c r="P43" s="83" t="inlineStr">
+        <is>
+          <t>M3
+P0 全完</t>
+        </is>
+      </c>
+      <c r="Q43" s="41" t="n"/>
+      <c r="R43" s="41" t="n"/>
+      <c r="S43" s="83" t="inlineStr">
+        <is>
+          <t>M4
+P1 第一波</t>
+        </is>
+      </c>
+      <c r="T43" s="43" t="n"/>
+      <c r="U43" s="43" t="n"/>
+      <c r="V43" s="43" t="n"/>
+      <c r="W43" s="84" t="inlineStr">
+        <is>
+          <t>M5
+P1 第二波</t>
+        </is>
+      </c>
+      <c r="X43" s="37" t="n"/>
+      <c r="Y43" s="37" t="n"/>
+      <c r="Z43" s="37" t="n"/>
+      <c r="AA43" s="84" t="inlineStr">
+        <is>
+          <t>M6
+P1 第三波</t>
+        </is>
+      </c>
+      <c r="AB43" s="39" t="n"/>
+      <c r="AC43" s="39" t="n"/>
+      <c r="AD43" s="85" t="inlineStr">
+        <is>
+          <t>M7
+品質達標</t>
+        </is>
+      </c>
+      <c r="AE43" s="39" t="n"/>
+      <c r="AF43" s="41" t="n"/>
+      <c r="AG43" s="41" t="n"/>
+      <c r="AH43" s="86" t="inlineStr">
+        <is>
+          <t>M8
+P2 完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="G45" s="87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  P0 核心流程</t>
+        </is>
+      </c>
+      <c r="H45" s="88" t="n"/>
+      <c r="I45" s="88" t="n"/>
+      <c r="K45" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  P1 業務擴展</t>
+        </is>
+      </c>
+      <c r="L45" s="90" t="n"/>
+      <c r="M45" s="90" t="n"/>
+      <c r="O45" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  P2 次優先</t>
+        </is>
+      </c>
+      <c r="P45" s="92" t="n"/>
+      <c r="Q45" s="92" t="n"/>
+      <c r="S45" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ◆ 里程碑截止</t>
+        </is>
+      </c>
+      <c r="T45" s="94" t="n"/>
+      <c r="U45" s="94" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="AB2:AE2"/>
+    <mergeCell ref="O45:Q45"/>
+    <mergeCell ref="S45:U45"/>
+    <mergeCell ref="A43:F43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="002F75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -4911,7 +7820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00375623"/>
@@ -11943,7 +14852,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C00"/>
@@ -11974,13 +14883,11 @@
           <t>📋 工作項統計</t>
         </is>
       </c>
-      <c r="B3" s="31" t="n"/>
       <c r="D3" s="30" t="inlineStr">
         <is>
           <t>🔌 API 統計</t>
         </is>
       </c>
-      <c r="E3" s="31" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
@@ -12070,13 +14977,11 @@
           <t>⏱ 時間線估算</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n"/>
       <c r="D11" s="30" t="inlineStr">
         <is>
           <t>👥 人員分工</t>
         </is>
       </c>
-      <c r="E11" s="31" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="32" t="inlineStr">
@@ -12194,13 +15099,11 @@
           <t>🏗 API 分布（按優先序）</t>
         </is>
       </c>
-      <c r="B19" s="31" t="n"/>
       <c r="D19" s="30" t="inlineStr">
         <is>
           <t>⚠️ 高風險模組</t>
         </is>
       </c>
-      <c r="E19" s="31" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
